--- a/Analysis/Sensitivity_alpha_sweep_gptoss.xlsx
+++ b/Analysis/Sensitivity_alpha_sweep_gptoss.xlsx
@@ -529,16 +529,16 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>0.27042</v>
+        <v>0.2724799999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.28974</v>
+        <v>0.29076</v>
       </c>
       <c r="H3" t="n">
-        <v>0.48</v>
+        <v>0.47386</v>
       </c>
       <c r="I3" t="n">
-        <v>0.76922</v>
+        <v>0.7651199999999999</v>
       </c>
       <c r="J3" t="n">
         <v>195</v>
@@ -567,13 +567,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>0.89666</v>
+        <v>0.8974400000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9107799999999999</v>
+        <v>0.9113599999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>0.91616</v>
+        <v>0.9173</v>
       </c>
       <c r="I4" t="n">
         <v>0.9812799999999999</v>
@@ -607,16 +607,16 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>0.04618</v>
+        <v>0.04545999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04565999999999999</v>
+        <v>0.04462000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3435800000000001</v>
+        <v>0.34254</v>
       </c>
       <c r="I5" t="n">
-        <v>0.67384</v>
+        <v>0.67282</v>
       </c>
       <c r="J5" t="n">
         <v>195</v>
@@ -647,16 +647,16 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0.25674</v>
+        <v>0.27044</v>
       </c>
       <c r="G6" t="n">
-        <v>0.27336</v>
+        <v>0.2841</v>
       </c>
       <c r="H6" t="n">
-        <v>0.4718</v>
+        <v>0.48104</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7651199999999999</v>
+        <v>0.7630799999999999</v>
       </c>
       <c r="J6" t="n">
         <v>195</v>
@@ -687,13 +687,13 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0.88658</v>
+        <v>0.89122</v>
       </c>
       <c r="G7" t="n">
-        <v>0.90152</v>
+        <v>0.90502</v>
       </c>
       <c r="H7" t="n">
-        <v>0.91378</v>
+        <v>0.92078</v>
       </c>
       <c r="I7" t="n">
         <v>0.9789999999999999</v>
@@ -767,16 +767,16 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0.27248</v>
+        <v>0.27454</v>
       </c>
       <c r="G9" t="n">
-        <v>0.29076</v>
+        <v>0.29284</v>
       </c>
       <c r="H9" t="n">
-        <v>0.48308</v>
+        <v>0.47694</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7682</v>
+        <v>0.76616</v>
       </c>
       <c r="J9" t="n">
         <v>195</v>
@@ -807,13 +807,13 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0.8974599999999999</v>
+        <v>0.8982199999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9120200000000001</v>
+        <v>0.9126</v>
       </c>
       <c r="H10" t="n">
-        <v>0.9173399999999999</v>
+        <v>0.91848</v>
       </c>
       <c r="I10" t="n">
         <v>0.98246</v>
@@ -847,16 +847,16 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0.04068000000000001</v>
+        <v>0.04271999999999999</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03845999999999999</v>
+        <v>0.04102</v>
       </c>
       <c r="H11" t="n">
-        <v>0.33334</v>
+        <v>0.33434</v>
       </c>
       <c r="I11" t="n">
-        <v>0.66462</v>
+        <v>0.66872</v>
       </c>
       <c r="J11" t="n">
         <v>195</v>
@@ -887,16 +887,16 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0.27042</v>
+        <v>0.27452</v>
       </c>
       <c r="G12" t="n">
-        <v>0.28974</v>
+        <v>0.29234</v>
       </c>
       <c r="H12" t="n">
-        <v>0.48</v>
+        <v>0.4769200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.76922</v>
+        <v>0.7651199999999999</v>
       </c>
       <c r="J12" t="n">
         <v>195</v>
@@ -927,16 +927,16 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0.89666</v>
+        <v>0.89978</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9107799999999999</v>
+        <v>0.9155000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>0.91616</v>
+        <v>0.9208000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9812799999999999</v>
+        <v>0.98594</v>
       </c>
       <c r="J13" t="n">
         <v>171.6</v>
@@ -967,16 +967,16 @@
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0.04271999999999999</v>
+        <v>0.04476000000000001</v>
       </c>
       <c r="G14" t="n">
-        <v>0.04204</v>
+        <v>0.0446</v>
       </c>
       <c r="H14" t="n">
-        <v>0.33744</v>
+        <v>0.33846</v>
       </c>
       <c r="I14" t="n">
-        <v>0.66976</v>
+        <v>0.6738600000000001</v>
       </c>
       <c r="J14" t="n">
         <v>195</v>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0.2752</v>
+        <v>0.27796</v>
       </c>
       <c r="G15" t="n">
-        <v>0.29384</v>
+        <v>0.29588</v>
       </c>
       <c r="H15" t="n">
-        <v>0.4851200000000001</v>
+        <v>0.48206</v>
       </c>
       <c r="I15" t="n">
-        <v>0.77436</v>
+        <v>0.77024</v>
       </c>
       <c r="J15" t="n">
         <v>195</v>
@@ -1047,16 +1047,16 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0.8927200000000001</v>
+        <v>0.8958199999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9096</v>
+        <v>0.91428</v>
       </c>
       <c r="H16" t="n">
-        <v>0.9103</v>
+        <v>0.915</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9812799999999999</v>
+        <v>0.98594</v>
       </c>
       <c r="J16" t="n">
         <v>171.6</v>
